--- a/domrf.xlsx
+++ b/domrf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shidlovskiyaf\projects\domrfparse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EE7868-DD9F-4E0A-92CC-F59326318F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD9F7C2-3DD0-4CF4-9AF8-5360DCC593A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>32274</t>
+  </si>
+  <si>
+    <t>44476</t>
+  </si>
+  <si>
+    <t>47114</t>
+  </si>
+  <si>
+    <t>48243</t>
+  </si>
+  <si>
+    <t>48706</t>
+  </si>
+  <si>
+    <t>49393</t>
+  </si>
+  <si>
+    <t>50218</t>
+  </si>
+  <si>
+    <t>50363</t>
+  </si>
+  <si>
+    <t>50364</t>
+  </si>
+  <si>
+    <t>50365</t>
+  </si>
+  <si>
+    <t>51725</t>
+  </si>
+  <si>
+    <t>52227</t>
+  </si>
+  <si>
+    <t>52790</t>
+  </si>
+  <si>
+    <t>52951</t>
+  </si>
+  <si>
+    <t>54528</t>
+  </si>
+  <si>
+    <t>55103</t>
+  </si>
+  <si>
+    <t>56363</t>
+  </si>
+  <si>
+    <t>60273</t>
+  </si>
+  <si>
+    <t>62087</t>
+  </si>
+  <si>
+    <t>66274</t>
+  </si>
+  <si>
+    <t>40970</t>
+  </si>
+  <si>
+    <t>46357</t>
+  </si>
+  <si>
+    <t>47115</t>
+  </si>
+  <si>
+    <t>30976</t>
+  </si>
+  <si>
+    <t>28023</t>
+  </si>
+  <si>
+    <t>38737</t>
+  </si>
+  <si>
+    <t>39428</t>
+  </si>
+  <si>
+    <t>38736</t>
+  </si>
+  <si>
+    <t>28158</t>
+  </si>
+  <si>
+    <t>11736</t>
+  </si>
+  <si>
+    <t>20370</t>
+  </si>
+  <si>
+    <t>28157</t>
+  </si>
+  <si>
+    <t>34938</t>
+  </si>
+  <si>
+    <t>28159</t>
+  </si>
+  <si>
+    <t>20369</t>
+  </si>
+  <si>
+    <t>20371</t>
+  </si>
+  <si>
+    <t>11734</t>
+  </si>
+  <si>
+    <t>11735</t>
+  </si>
+  <si>
+    <t>30176</t>
   </si>
 </sst>
 </file>
@@ -395,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}">
-  <dimension ref="B1:B2"/>
+  <dimension ref="B1:B40"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
@@ -404,8 +521,198 @@
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2">
-        <v>65172</v>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/domrf.xlsx
+++ b/domrf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shidlovskiyaf\projects\domrfparse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD9F7C2-3DD0-4CF4-9AF8-5360DCC593A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19754262-882C-4FB9-AF80-4B4A370FDA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -72,9 +72,6 @@
     <t>50364</t>
   </si>
   <si>
-    <t>50365</t>
-  </si>
-  <si>
     <t>51725</t>
   </si>
   <si>
@@ -90,76 +87,16 @@
     <t>54528</t>
   </si>
   <si>
-    <t>55103</t>
-  </si>
-  <si>
     <t>56363</t>
   </si>
   <si>
-    <t>60273</t>
-  </si>
-  <si>
     <t>62087</t>
   </si>
   <si>
     <t>66274</t>
   </si>
   <si>
-    <t>40970</t>
-  </si>
-  <si>
-    <t>46357</t>
-  </si>
-  <si>
-    <t>47115</t>
-  </si>
-  <si>
-    <t>30976</t>
-  </si>
-  <si>
-    <t>28023</t>
-  </si>
-  <si>
-    <t>38737</t>
-  </si>
-  <si>
-    <t>39428</t>
-  </si>
-  <si>
-    <t>38736</t>
-  </si>
-  <si>
-    <t>28158</t>
-  </si>
-  <si>
-    <t>11736</t>
-  </si>
-  <si>
-    <t>20370</t>
-  </si>
-  <si>
-    <t>28157</t>
-  </si>
-  <si>
-    <t>34938</t>
-  </si>
-  <si>
-    <t>28159</t>
-  </si>
-  <si>
-    <t>20369</t>
-  </si>
-  <si>
-    <t>20371</t>
-  </si>
-  <si>
-    <t>11734</t>
-  </si>
-  <si>
-    <t>11735</t>
-  </si>
-  <si>
-    <t>30176</t>
+    <t>58749</t>
   </si>
 </sst>
 </file>
@@ -512,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}">
-  <dimension ref="B1:B40"/>
+  <dimension ref="B1:B19"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
@@ -522,32 +459,32 @@
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
@@ -557,162 +494,57 @@
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/domrf.xlsx
+++ b/domrf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shidlovskiyaf\projects\domrfparse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19754262-882C-4FB9-AF80-4B4A370FDA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3291E6-3E17-45B6-A42C-A8330F52394F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
   </bookViews>
@@ -40,63 +40,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>32274</t>
-  </si>
-  <si>
-    <t>44476</t>
-  </si>
-  <si>
-    <t>47114</t>
-  </si>
-  <si>
-    <t>48243</t>
-  </si>
-  <si>
-    <t>48706</t>
-  </si>
-  <si>
-    <t>49393</t>
-  </si>
-  <si>
-    <t>50218</t>
-  </si>
-  <si>
-    <t>50363</t>
-  </si>
-  <si>
-    <t>50364</t>
-  </si>
-  <si>
-    <t>51725</t>
-  </si>
-  <si>
-    <t>52227</t>
-  </si>
-  <si>
-    <t>52790</t>
-  </si>
-  <si>
-    <t>52951</t>
-  </si>
-  <si>
-    <t>54528</t>
-  </si>
-  <si>
-    <t>56363</t>
-  </si>
-  <si>
-    <t>62087</t>
-  </si>
-  <si>
-    <t>66274</t>
-  </si>
-  <si>
-    <t>58749</t>
+    <t>70300</t>
+  </si>
+  <si>
+    <t>70309</t>
+  </si>
+  <si>
+    <t>70310</t>
+  </si>
+  <si>
+    <t>70368</t>
+  </si>
+  <si>
+    <t>70374</t>
+  </si>
+  <si>
+    <t>70416</t>
+  </si>
+  <si>
+    <t>70442</t>
+  </si>
+  <si>
+    <t>70547</t>
+  </si>
+  <si>
+    <t>70548</t>
+  </si>
+  <si>
+    <t>70585</t>
+  </si>
+  <si>
+    <t>70590</t>
+  </si>
+  <si>
+    <t>70610</t>
+  </si>
+  <si>
+    <t>70663</t>
+  </si>
+  <si>
+    <t>70684</t>
+  </si>
+  <si>
+    <t>70718</t>
+  </si>
+  <si>
+    <t>70778</t>
+  </si>
+  <si>
+    <t>70783</t>
   </si>
 </sst>
 </file>
@@ -449,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}">
-  <dimension ref="B1:B19"/>
+  <dimension ref="B1:B18"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
@@ -459,32 +456,32 @@
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
@@ -494,57 +491,52 @@
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/domrf.xlsx
+++ b/domrf.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shidlovskiyaf\projects\domrfparse\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arkadijsidlovskij/Desktop/projects/samples_forma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3291E6-3E17-45B6-A42C-A8330F52394F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9432642C-9F99-CF47-B8DE-AB444C3FAE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$B$1:$B$648</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sheet1!$B$1:$B$648</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -94,13 +92,322 @@
   </si>
   <si>
     <t>70783</t>
+  </si>
+  <si>
+    <t>Artel / Электрозаводская, 60 / Candles</t>
+  </si>
+  <si>
+    <t>58524</t>
+  </si>
+  <si>
+    <t>Life Time / ONEST</t>
+  </si>
+  <si>
+    <t>46310</t>
+  </si>
+  <si>
+    <t>TATE</t>
+  </si>
+  <si>
+    <t>56210</t>
+  </si>
+  <si>
+    <t>Верейская 41</t>
+  </si>
+  <si>
+    <t>45184</t>
+  </si>
+  <si>
+    <t>45185</t>
+  </si>
+  <si>
+    <t>64768</t>
+  </si>
+  <si>
+    <t>Дом Франка</t>
+  </si>
+  <si>
+    <t>51567</t>
+  </si>
+  <si>
+    <t>Молжаниново</t>
+  </si>
+  <si>
+    <t>54505</t>
+  </si>
+  <si>
+    <t>54541</t>
+  </si>
+  <si>
+    <t>56071</t>
+  </si>
+  <si>
+    <t>Новые Академики</t>
+  </si>
+  <si>
+    <t>56953</t>
+  </si>
+  <si>
+    <t>Преображенская площадь</t>
+  </si>
+  <si>
+    <t>57807</t>
+  </si>
+  <si>
+    <t>46646</t>
+  </si>
+  <si>
+    <t>53519</t>
+  </si>
+  <si>
+    <t>50365</t>
+  </si>
+  <si>
+    <t>Театральный квартал</t>
+  </si>
+  <si>
+    <t>40159</t>
+  </si>
+  <si>
+    <t>49678</t>
+  </si>
+  <si>
+    <t>51931</t>
+  </si>
+  <si>
+    <t>51932</t>
+  </si>
+  <si>
+    <t>River Park Коломенское (Фаза 2) (паркинг / коммерция)</t>
+  </si>
+  <si>
+    <t>64375</t>
+  </si>
+  <si>
+    <t>Бестселлер</t>
+  </si>
+  <si>
+    <t>65192</t>
+  </si>
+  <si>
+    <t>Садовническая 69</t>
+  </si>
+  <si>
+    <t>62431</t>
+  </si>
+  <si>
+    <t>68822</t>
+  </si>
+  <si>
+    <t>45519</t>
+  </si>
+  <si>
+    <t>53661</t>
+  </si>
+  <si>
+    <t>48994</t>
+  </si>
+  <si>
+    <t>Малевич</t>
+  </si>
+  <si>
+    <t>46510</t>
+  </si>
+  <si>
+    <t>51218</t>
+  </si>
+  <si>
+    <t>Форум / Forum</t>
+  </si>
+  <si>
+    <t>51237</t>
+  </si>
+  <si>
+    <t>Люче / Luce</t>
+  </si>
+  <si>
+    <t>53669</t>
+  </si>
+  <si>
+    <t>Слава / SLAVA</t>
+  </si>
+  <si>
+    <t>53747</t>
+  </si>
+  <si>
+    <t>Николь / Nicole</t>
+  </si>
+  <si>
+    <t>55103</t>
+  </si>
+  <si>
+    <t>НОВА / NOVA</t>
+  </si>
+  <si>
+    <t>58150</t>
+  </si>
+  <si>
+    <t>СИТИДЗЕН / Cityzen</t>
+  </si>
+  <si>
+    <t>57752</t>
+  </si>
+  <si>
+    <t>67615</t>
+  </si>
+  <si>
+    <t>ДИУС / DIUS</t>
+  </si>
+  <si>
+    <t>57838</t>
+  </si>
+  <si>
+    <t>Сет / SET</t>
+  </si>
+  <si>
+    <t>61562</t>
+  </si>
+  <si>
+    <t>ОНЕ / One</t>
+  </si>
+  <si>
+    <t>68245</t>
+  </si>
+  <si>
+    <t>Vesper Погодинская</t>
+  </si>
+  <si>
+    <t>70225</t>
+  </si>
+  <si>
+    <t>42848</t>
+  </si>
+  <si>
+    <t>БРЮСОВ / BRUSOV</t>
+  </si>
+  <si>
+    <t>50291</t>
+  </si>
+  <si>
+    <t>Кинг &amp; Санс / King &amp; Sons Residence</t>
+  </si>
+  <si>
+    <t>57465</t>
+  </si>
+  <si>
+    <t>Мариин Парк / Mariinn Park</t>
+  </si>
+  <si>
+    <t>63924</t>
+  </si>
+  <si>
+    <t>44646</t>
+  </si>
+  <si>
+    <t>50420</t>
+  </si>
+  <si>
+    <t>51108</t>
+  </si>
+  <si>
+    <t>51119</t>
+  </si>
+  <si>
+    <t>53412</t>
+  </si>
+  <si>
+    <t>53413</t>
+  </si>
+  <si>
+    <t>53542</t>
+  </si>
+  <si>
+    <t>53618</t>
+  </si>
+  <si>
+    <t>53889</t>
+  </si>
+  <si>
+    <t>56307</t>
+  </si>
+  <si>
+    <t>56944</t>
+  </si>
+  <si>
+    <t>56949</t>
+  </si>
+  <si>
+    <t>58299</t>
+  </si>
+  <si>
+    <t>66242</t>
+  </si>
+  <si>
+    <t>Taller [офис]</t>
+  </si>
+  <si>
+    <t>43701</t>
+  </si>
+  <si>
+    <t>QOOB [офис]</t>
+  </si>
+  <si>
+    <t>54664</t>
+  </si>
+  <si>
+    <t>AVIUM [Офисы]</t>
+  </si>
+  <si>
+    <t>65172</t>
+  </si>
+  <si>
+    <t>65640</t>
+  </si>
+  <si>
+    <t>Новая звезда 2 [не Москва]</t>
+  </si>
+  <si>
+    <t>66399</t>
+  </si>
+  <si>
+    <t>66400</t>
+  </si>
+  <si>
+    <t>Г. Москва, СВАО, ул.Полярная, з/у 16 [Реновация]</t>
+  </si>
+  <si>
+    <t>66982</t>
+  </si>
+  <si>
+    <t>Жилой дом г.Москва Дмитровское ш. з/у 89 [Реновация]</t>
+  </si>
+  <si>
+    <t>54732</t>
+  </si>
+  <si>
+    <t>Юнино [не москва]</t>
+  </si>
+  <si>
+    <t>58056</t>
+  </si>
+  <si>
+    <t>1-й Саларьевский [не москва]</t>
+  </si>
+  <si>
+    <t>60896</t>
+  </si>
+  <si>
+    <t>62055</t>
+  </si>
+  <si>
+    <t>62843</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -109,16 +416,36 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor theme="9" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -126,12 +453,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.79998168889431442"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.79998168889431442"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.79998168889431442"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -150,9 +509,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -190,7 +549,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -296,7 +655,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -438,103 +797,628 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D901455-D2E7-5D4E-A4A6-7B3CB456779A}">
+  <dimension ref="A1:A103"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}">
   <dimension ref="B1:B18"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>17</v>
       </c>
